--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.30995575835044</v>
+        <v>2.000367810731946</v>
       </c>
       <c r="D2" t="n">
-        <v>12.30995575835044</v>
+        <v>2.000367810731946</v>
       </c>
       <c r="E2" t="n">
-        <v>3.318874315550961</v>
+        <v>0.5393170762770314</v>
       </c>
       <c r="F2" t="n">
-        <v>3.35185692476288</v>
+        <v>0.5446767502739682</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.94770438945236</v>
+        <v>3.079001963286009</v>
       </c>
       <c r="D3" t="n">
-        <v>19.0136696078762</v>
+        <v>3.089721311279883</v>
       </c>
       <c r="E3" t="n">
-        <v>3.318874315550961</v>
+        <v>0.5393170762770314</v>
       </c>
       <c r="F3" t="n">
-        <v>3.35185692476288</v>
+        <v>0.5446767502739682</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
